--- a/designs/燎原火-许定_暗夜潜行_关卡设计.xlsx
+++ b/designs/燎原火-许定_暗夜潜行_关卡设计.xlsx
@@ -11,6 +11,7 @@
     <sheet name="角色配置表" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="物品机关表" sheetId="3" state="visible" r:id="rId3"/>
     <sheet name="机制说明" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="机关怪物表" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1764,4 +1765,942 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I21"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="4" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
+    <col width="4" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="6" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>编号</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>地图标识</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>朝向</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>实例ID</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>类型</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>初始位置(X,Y)</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>血量</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>特效</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>行为树</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>甲</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>右</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>guard_001</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>守卫</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>(1,11)</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>视野范围3格</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>巡逻路线A：甲→乙→丙</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>乙</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>下</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>guard_002</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>守卫</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>(7,19)</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>视野范围3格</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>巡逻路线B：乙→丁</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>丙</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>左</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>guard_003</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>守卫</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>(7,11)</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>视野范围3格,携带钥匙</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>巡逻路线C：丙→戊</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>丁</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>上</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>guard_004</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>守卫</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>(1,15)</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>视野范围3格</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>巡逻路线D：丁→己</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>戊</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>右</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>guard_005</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>守卫</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>(7,15)</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>视野范围3格</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>巡逻路线E：戊→书房</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>己</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>左</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>guard_006</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>守卫</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>(1,19)</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1500</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>视野范围3格</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>巡逻路线F：己→营帐</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>刺</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>随机</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>assassin_001</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>刺客</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>(3,9)</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>阴影隐形,暴露值&gt;50%显形</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>追击暴露玩家</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>刺</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>随机</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>assassin_002</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>刺客</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>(1,7)</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>阴影隐形,暴露值&gt;50%显形</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>追击暴露玩家</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>刺</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>随机</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>assassin_003</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>刺客</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>(5,7)</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>阴影隐形,暴露值&gt;50%显形</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>追击暴露玩家</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>刺</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>随机</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>assassin_004</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>刺客</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>(1,5)</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>阴影隐形,暴露值&gt;50%显形</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>追击暴露玩家</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>刺</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>随机</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>assassin_005</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>刺客</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>(5,5)</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>阴影隐形,暴露值&gt;50%显形</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>追击暴露玩家</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>刺</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>随机</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>assassin_006</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>刺客</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>(3,9)</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>1800</v>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>阴影隐形,暴露值&gt;50%显形</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>追击暴露玩家</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>刺头</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>下</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>assassin_boss</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>刺客头目</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>(3,9)</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>2200</v>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>阴影隐形,携带信件3</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>保护信件3,追击暴露玩家</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>栅</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>gate_001</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>栅栏</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>(0,20)</t>
+        </is>
+      </c>
+      <c r="G15" t="n">
+        <v>9999</v>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>不可穿越,阻挡视线</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>静态障碍</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>栅</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>gate_002</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>栅栏</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>(9,20)</t>
+        </is>
+      </c>
+      <c r="G16" t="n">
+        <v>9999</v>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>不可穿越,阻挡视线</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>静态障碍</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>门</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>door_001</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>营帐门</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>(3,19)</t>
+        </is>
+      </c>
+      <c r="G17" t="n">
+        <v>800</v>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>可破坏,内有信件1</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>被攻击后开启</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>门</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>door_002</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>书房门</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>(4,17)</t>
+        </is>
+      </c>
+      <c r="G18" t="n">
+        <v>800</v>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>需钥匙开启,内有信件2</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>需钥匙</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>阴</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>shadow_001</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>阴影区</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>多处</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>玩家隐形,刺客隐藏</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>区域效果</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>火</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>item_001</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>火把</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>随机</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>照亮黑暗,吸引守卫</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>拾取使用</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>酒</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>item_002</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>酒</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>随机</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>迷晕守卫(一次性)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>拾取使用</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>